--- a/Zomato/src/test/resources/testData/zomato.xlsx
+++ b/Zomato/src/test/resources/testData/zomato.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loges\MynewWorkspace-2025\Zomato\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loges\git\repository5\Zomato\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404BACFF-2049-4FE4-A835-D5609101E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B07BB8-F768-4F53-A588-21A81F234A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -347,6 +347,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="67.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/Zomato/src/test/resources/testData/zomato.xlsx
+++ b/Zomato/src/test/resources/testData/zomato.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loges\git\repository5\Zomato\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B07BB8-F768-4F53-A588-21A81F234A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277C21A-6A3D-46AA-8ABA-20E66652AA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Gsr Men's Hostel,Bharathiyar Street,PTC Quarters,Thuraipakkam,chennai-600097</t>
+    <t>Shanti Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>2/13, Ground Floor, Rehinus Street, Opposite Hockey Stadium, Shanti Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Rehinus Street</t>
   </si>
 </sst>
 </file>
@@ -345,18 +351,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="67.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="2" max="2" width="71.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>